--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488202_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488202_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>Y. VAQUERO HERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8048</v>
+        <v>2.3444</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4001</v>
+        <v>0.2076</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5953000000000001</v>
+        <v>2.1367</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5023</v>
+        <v>0.0182</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.527</v>
+        <v>-1.7729</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0246</v>
+        <v>1.7911</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2862</v>
+        <v>-0.3445</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1926</v>
+        <v>-1.091</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0936</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7885</v>
+        <v>0.3627</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7196</v>
+        <v>-0.6818</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.06900000000000001</v>
+        <v>1.0446</v>
       </c>
       <c r="P2" t="n">
         <v>0.9264</v>
@@ -610,28 +610,28 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6395</v>
+        <v>0.7698</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7994</v>
+        <v>0.5521</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8401</v>
+        <v>0.2176</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5733</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. VAQUERO HERNANDEZ</t>
+          <t>O. KANTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4378</v>
+        <v>1.0592</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5758</v>
+        <v>2.6708</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0136</v>
+        <v>-1.6116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0182</v>
+        <v>2.406</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7729</v>
+        <v>1.019</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7911</v>
+        <v>1.387</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3445</v>
+        <v>2.9251</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.091</v>
+        <v>2.1679</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7572</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3627</v>
+        <v>-0.5191</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6818</v>
+        <v>-1.149</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0446</v>
+        <v>0.6299</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1368</v>
+        <v>0.6886</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2313</v>
+        <v>0.0606</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0945</v>
+        <v>0.628</v>
       </c>
       <c r="V3" t="n">
-        <v>0.63</v>
+        <v>-3.1471</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X3" t="n">
-        <v>0.63</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. KANTE</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0844</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5728</v>
+        <v>1.8611</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4885</v>
+        <v>-1.1025</v>
       </c>
       <c r="G4" t="n">
-        <v>2.406</v>
+        <v>-0.4166</v>
       </c>
       <c r="H4" t="n">
-        <v>1.019</v>
+        <v>1.4189</v>
       </c>
       <c r="I4" t="n">
-        <v>1.387</v>
+        <v>-1.8354</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9251</v>
+        <v>1.4943</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1679</v>
+        <v>1.4943</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7572</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5191</v>
+        <v>-1.9108</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.149</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6299</v>
+        <v>-1.8354</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7138</v>
+        <v>0.434</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0373</v>
+        <v>0.3669</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7511</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5616</v>
+        <v>0.1447</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8611</v>
+        <v>1.8215</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2995</v>
+        <v>-1.6768</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4166</v>
+        <v>1.2666</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4189</v>
+        <v>1.1989</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8354</v>
+        <v>0.0677</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4943</v>
+        <v>3.6506</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4943</v>
+        <v>2.9456</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9108</v>
+        <v>-2.384</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-1.7467</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8354</v>
+        <v>-0.6373</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>-1.297</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.237</v>
+        <v>1.1195</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3669</v>
+        <v>0.6358</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1298</v>
+        <v>0.4837</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9444</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4374</v>
+        <v>0.0152</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3112</v>
+        <v>1.0291</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8738</v>
+        <v>-1.0139</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2666</v>
+        <v>-0.5023</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1989</v>
+        <v>-0.527</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0677</v>
+        <v>0.0246</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6506</v>
+        <v>0.2862</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9456</v>
+        <v>0.1926</v>
       </c>
       <c r="L8" t="n">
-        <v>0.705</v>
+        <v>0.0936</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.384</v>
+        <v>-0.7885</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7467</v>
+        <v>-0.7196</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6373</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4122</v>
+        <v>0.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1254</v>
+        <v>0.4284</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2867</v>
+        <v>0.4215</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9444</v>
+        <v>-1.2589</v>
       </c>
       <c r="W8" t="n">
         <v>0.3144</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. KONE</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.7127</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8318</v>
+        <v>-0.572</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9149</v>
+        <v>-0.1407</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8357</v>
+        <v>-2.9348</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0801</v>
+        <v>-2.0392</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7556</v>
+        <v>-0.8955</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3359</v>
+        <v>-2.1922</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4983</v>
+        <v>-0.928</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8342</v>
+        <v>-1.2643</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4998</v>
+        <v>-0.7426</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5784</v>
+        <v>-1.1113</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9214</v>
+        <v>0.3687</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4371</v>
+        <v>0.2602</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0942</v>
+        <v>0.0289</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3429</v>
+        <v>0.2313</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3155</v>
+        <v>2.5177</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>S. KONE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8095</v>
+        <v>-1.308</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8658</v>
+        <v>-0.2454</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0563</v>
+        <v>-1.0626</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9348</v>
+        <v>-2.8357</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0392</v>
+        <v>-0.0801</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8955</v>
+        <v>-2.7556</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1922</v>
+        <v>-0.3359</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.928</v>
+        <v>1.4983</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2643</v>
+        <v>-1.8342</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7426</v>
+        <v>-2.4998</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1113</v>
+        <v>-1.5784</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3687</v>
+        <v>-0.9214</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1634</v>
+        <v>1.2121</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2649</v>
+        <v>1.0169</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4283</v>
+        <v>0.1952</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5177</v>
+        <v>0.3155</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2754</v>
+        <v>-4.1977</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5774</v>
+        <v>-2.5981</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.698</v>
+        <v>-1.5995</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5678</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9491000000000001</v>
+        <v>0.1287</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.195</v>
+        <v>-0.2157</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2459</v>
+        <v>0.3444</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5015</v>
+        <v>-6.8887</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2576</v>
+        <v>-2.7679</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.2439</v>
+        <v>-4.1208</v>
       </c>
       <c r="G12" t="n">
         <v>-5.299</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8145</v>
+        <v>-0.2018</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.052</v>
+        <v>-0.5624</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2375</v>
+        <v>0.3606</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5733</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5426</v>
+        <v>-7.1011</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0195</v>
+        <v>-4.7258</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5231</v>
+        <v>-2.3753</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9859</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.5419</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9762</v>
+        <v>-0.6824</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0072</v>
+        <v>0.1405</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5733</v>
@@ -1504,10 +1504,10 @@
         <v>-14.5979</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.030900000000001</v>
+        <v>-2.0309</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.5671</v>
+        <v>-12.567</v>
       </c>
       <c r="G14" t="n">
         <v>-14.5631</v>
@@ -1522,7 +1522,7 @@
         <v>1.5318</v>
       </c>
       <c r="K14" t="n">
-        <v>3.568199999999998</v>
+        <v>3.568199999999999</v>
       </c>
       <c r="L14" t="n">
         <v>-2.0366</v>
@@ -1549,10 +1549,10 @@
         <v>4.719199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6292</v>
+        <v>1.6291</v>
       </c>
       <c r="U14" t="n">
-        <v>3.09</v>
+        <v>3.089899999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-6.607099999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4648</v>
+        <v>5.4334</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0086</v>
+        <v>3.5916</v>
       </c>
       <c r="F15" t="n">
-        <v>3.4562</v>
+        <v>1.8417</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8042</v>
+        <v>4.3705</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4293</v>
+        <v>2.4414</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3749</v>
+        <v>1.929</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5473</v>
+        <v>3.8818</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9099</v>
+        <v>1.8378</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3626</v>
+        <v>2.044</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2569</v>
+        <v>0.4886</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5195</v>
+        <v>0.6036</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.115</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0323</v>
+        <v>-0.2341</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3889</v>
+        <v>-0.6047</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6434</v>
+        <v>0.3705</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0011</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0011</v>
+        <v>0.3144</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2812</v>
+        <v>3.4439</v>
       </c>
       <c r="E16" t="n">
-        <v>3.102</v>
+        <v>0.2459</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1792</v>
+        <v>3.198</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3705</v>
+        <v>1.8042</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4414</v>
+        <v>1.4293</v>
       </c>
       <c r="I16" t="n">
-        <v>1.929</v>
+        <v>0.3749</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8818</v>
+        <v>0.5473</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8378</v>
+        <v>0.9099</v>
       </c>
       <c r="L16" t="n">
-        <v>2.044</v>
+        <v>-0.3626</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4886</v>
+        <v>1.2569</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6036</v>
+        <v>0.5195</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.115</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3863</v>
+        <v>2.0114</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0943</v>
+        <v>0.6261</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.292</v>
+        <v>1.3853</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.0011</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>-0.0011</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0157</v>
+        <v>3.2351</v>
       </c>
       <c r="E17" t="n">
         <v>2.5977</v>
       </c>
       <c r="F17" t="n">
-        <v>0.418</v>
+        <v>0.6374</v>
       </c>
       <c r="G17" t="n">
         <v>2.9798</v>
@@ -1780,13 +1780,13 @@
         <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4818</v>
+        <v>-0.2624</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4414</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0403</v>
+        <v>0.179</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6695</v>
+        <v>3.2009</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9288</v>
+        <v>1.0268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7406</v>
+        <v>2.1741</v>
       </c>
       <c r="G18" t="n">
         <v>2.8368</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1674</v>
+        <v>0.364</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0032</v>
+        <v>0.4303</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2948</v>
+        <v>1.9957</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4236</v>
+        <v>3.0112</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1288</v>
+        <v>-1.0154</v>
       </c>
       <c r="G19" t="n">
         <v>1.9496</v>
@@ -1936,13 +1936,13 @@
         <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4129</v>
+        <v>-0.7119</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2584</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1545</v>
+        <v>-0.0411</v>
       </c>
       <c r="V19" t="n">
         <v>0.9433</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4536</v>
+        <v>1.616</v>
       </c>
       <c r="E20" t="n">
         <v>0.8972</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4436</v>
+        <v>0.7189</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9612000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1585</v>
+        <v>-0.9961</v>
       </c>
       <c r="T20" t="n">
         <v>-0.7697000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3888</v>
+        <v>-0.2264</v>
       </c>
       <c r="V20" t="n">
         <v>2.8321</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.1301</v>
       </c>
       <c r="E21" t="n">
-        <v>0.773</v>
+        <v>0.8709</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.336</v>
+        <v>-1.001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0487</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6059</v>
+        <v>-1.173</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.766</v>
+        <v>-0.6681</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8399</v>
+        <v>-0.5049</v>
       </c>
       <c r="V21" t="n">
         <v>2.8327</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0186</v>
+        <v>-0.9328</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1639</v>
+        <v>0.3257</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8547</v>
+        <v>-1.2585</v>
       </c>
       <c r="G22" t="n">
         <v>2.6319</v>
@@ -2170,13 +2170,13 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5388</v>
+        <v>-0.453</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9849</v>
+        <v>-0.4952</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5538999999999999</v>
+        <v>0.0423</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.598</v>
+        <v>17.8621</v>
       </c>
       <c r="E23" t="n">
         <v>12.567</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0309</v>
+        <v>5.2952</v>
       </c>
       <c r="G23" t="n">
         <v>14.5629</v>
@@ -2248,13 +2248,13 @@
         <v>8.337900000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.7193</v>
+        <v>-1.4551</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.089900000000001</v>
+        <v>-3.090100000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6292</v>
+        <v>1.635</v>
       </c>
       <c r="V23" t="n">
         <v>6.607</v>
